--- a/output/Glen_Brook/TestEnvData_Database.xlsx
+++ b/output/Glen_Brook/TestEnvData_Database.xlsx
@@ -493,7 +493,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E2" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="3">
@@ -510,7 +510,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E3" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="4">
@@ -527,7 +527,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E4" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="5">
@@ -544,7 +544,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E5" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="6">
@@ -561,7 +561,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E6" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="7">
@@ -578,7 +578,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E7" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="8">
@@ -595,7 +595,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E8" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="9">
@@ -612,7 +612,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E9" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="10">
@@ -629,7 +629,7 @@
         <v>NDC SWEEP FAC</v>
       </c>
       <c r="E10" t="str">
-        <v>GLEN BROOK REHABILITATION XXXXXX2969</v>
+        <v>Analyzed Checking XXXXXX2969</v>
       </c>
     </row>
     <row r="11">
@@ -811,38 +811,111 @@
         <v>07/01/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>07/02/2025</v>
+        <v>07/01/2025</v>
       </c>
       <c r="C2" t="str">
-        <v>$2,508.93</v>
+        <v>$182.65</v>
       </c>
       <c r="D2" t="str">
-        <v>$2,508.93</v>
+        <v>$182.65</v>
       </c>
       <c r="E2" t="str">
-        <v>ACH 7/1/2025</v>
+        <v>RFMS 7/1/2025</v>
       </c>
       <c r="F2" t="str">
-        <v>BANKCARD BTOT DEP</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G2" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="3" xml:space="preserve">
+    <row r="3">
       <c r="A3" t="str">
         <v>07/01/2025</v>
       </c>
       <c r="B3" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="C3" t="str">
+        <v>$2,508.93</v>
+      </c>
+      <c r="D3" t="str">
+        <v>$2,508.93</v>
+      </c>
+      <c r="E3" t="str">
+        <v>ACH 7/1/2025</v>
+      </c>
+      <c r="F3" t="str">
+        <v>BANKCARD BTOT DEP</v>
+      </c>
+      <c r="G3" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
+      <c r="A4" t="str">
         <v>07/01/2025</v>
       </c>
-      <c r="C3" t="str">
+      <c r="B4" t="str">
+        <v>07/02/2025</v>
+      </c>
+      <c r="C4" t="str">
+        <v>$3,151.07</v>
+      </c>
+      <c r="D4" t="str">
+        <v>$3,151.07</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $1,653.07 (ACH 7/1/2025 | 7/1)
+2: $1,498.00 (ACH 7/1/2025 | 7/1)</v>
+      </c>
+      <c r="F4" t="str">
+        <v>Glen Brook Rehab Settlement</v>
+      </c>
+      <c r="G4" t="str">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
+      <c r="A5" t="str" xml:space="preserve">
+        <v xml:space="preserve">07/01/2025
+-
+07/04/2025</v>
+      </c>
+      <c r="B5" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="C5" t="str">
+        <v>$11,386.84</v>
+      </c>
+      <c r="D5" t="str">
+        <v>$11,386.84</v>
+      </c>
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: -$4,181.62 (PAHW 07/01/25 B#4901&amp;4934 Really $11,386.84 | 7/1)
+2: $15,568.46 (PAHW 07/04/25 B#4901&amp;4934 Really $11,386.84 | 7/4)</v>
+      </c>
+      <c r="F5" t="str">
+        <v>HCCLAIMPMT PA CLAIMS TRN* * * \</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
+      <c r="A6" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="B6" t="str">
+        <v>07/01/2025</v>
+      </c>
+      <c r="C6" t="str">
         <v>$18,905.87</v>
       </c>
-      <c r="D3" t="str">
+      <c r="D6" t="str">
         <v>$18,905.87</v>
       </c>
-      <c r="E3" t="str" xml:space="preserve">
+      <c r="E6" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $1,223.00 (ACH 6/29/2025 | 7/1)
 2: $50.00 (ACH 6/28/2025 | 7/1)
 3: $11,700.00 (ACH 6/28/2025 | 7/1)
@@ -850,84 +923,11 @@
 5: $473.99 (ACH 6/30/2025 | 7/1)
 6: $1,223.00 (ACH 06/29/2025 | 7/1)</v>
       </c>
-      <c r="F3" t="str">
+      <c r="F6" t="str">
         <v>Glen Brook Rehab Settlement</v>
       </c>
-      <c r="G3" t="str">
+      <c r="G6" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="4" xml:space="preserve">
-      <c r="A4" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B4" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C4" t="str">
-        <v>$3,151.07</v>
-      </c>
-      <c r="D4" t="str">
-        <v>$3,151.07</v>
-      </c>
-      <c r="E4" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $1,653.07 (ACH 7/1/2025 | 7/1)
-2: $1,498.00 (ACH 7/1/2025 | 7/1)</v>
-      </c>
-      <c r="F4" t="str">
-        <v>Glen Brook Rehab Settlement</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="5" xml:space="preserve">
-      <c r="A5" t="str" xml:space="preserve">
-        <v xml:space="preserve">07/01/2025
--
-07/04/2025</v>
-      </c>
-      <c r="B5" t="str">
-        <v>07/08/2025</v>
-      </c>
-      <c r="C5" t="str">
-        <v>$11,386.84</v>
-      </c>
-      <c r="D5" t="str">
-        <v>$11,386.84</v>
-      </c>
-      <c r="E5" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $-4,181.62 (PAHW 07/01/25 B#4901&amp;4934 Really $11,386.84 | 7/1)
-2: $15,568.46 (PAHW 07/04/25 B#4901&amp;4934 Really $11,386.84 | 7/4)</v>
-      </c>
-      <c r="F5" t="str">
-        <v>HCCLAIMPMT PA CLAIMS TRN* * * \</v>
-      </c>
-      <c r="G5" t="str">
-        <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>07/01/2025</v>
-      </c>
-      <c r="B6" t="str">
-        <v>07/02/2025</v>
-      </c>
-      <c r="C6" t="str">
-        <v>$33,571.90</v>
-      </c>
-      <c r="D6" t="str">
-        <v>$33,571.90</v>
-      </c>
-      <c r="E6" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/01/2025</v>
-      </c>
-      <c r="F6" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
-      </c>
-      <c r="G6" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="7">
@@ -935,47 +935,45 @@
         <v>07/01/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>07/01/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="C7" t="str">
-        <v>$182.65</v>
+        <v>$33,571.90</v>
       </c>
       <c r="D7" t="str">
-        <v>$182.65</v>
+        <v>$33,571.90</v>
       </c>
       <c r="E7" t="str">
-        <v>RFMS 7/1/2025</v>
+        <v>WPS GHA - MAC J5 PART A 07/01/2025</v>
       </c>
       <c r="F7" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G7" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="8" xml:space="preserve">
+    <row r="8">
       <c r="A8" t="str">
         <v>07/02/2025</v>
       </c>
       <c r="B8" t="str">
-        <v>07/03/2025</v>
+        <v>07/02/2025</v>
       </c>
       <c r="C8" t="str">
-        <v>$17,930.91</v>
+        <v>$95.01</v>
       </c>
       <c r="D8" t="str">
-        <v>$17,930.91</v>
-      </c>
-      <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $30.00 (ACH 7/2/2025 | 7/2)
-2: $17,900.91 (Deposit 7/2/2025 | 7/2)</v>
-      </c>
-      <c r="F8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $6,022.00 (Glen Brook Rehab Settlement | 7/3)
-2: $11,908.91 (Glen Brook Rehab Settlement | 7/3)</v>
+        <v>$95.01</v>
+      </c>
+      <c r="E8" t="str">
+        <v>AETNA 07/02/2025</v>
+      </c>
+      <c r="F8" t="str">
+        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
       </c>
       <c r="G8" t="str">
-        <v>Many-to-Many</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="9">
@@ -986,16 +984,16 @@
         <v>07/02/2025</v>
       </c>
       <c r="C9" t="str">
-        <v>$95.01</v>
+        <v>$111.86</v>
       </c>
       <c r="D9" t="str">
-        <v>$95.01</v>
+        <v>$111.86</v>
       </c>
       <c r="E9" t="str">
-        <v>AETNA 07/02/2025</v>
+        <v>VETERAN FAMILY MEMBER PROGRAM 07/02/2025</v>
       </c>
       <c r="F9" t="str">
-        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
+        <v>TREAS MISC PAY</v>
       </c>
       <c r="G9" t="str">
         <v>Exact</v>
@@ -1009,16 +1007,16 @@
         <v>07/02/2025</v>
       </c>
       <c r="C10" t="str">
-        <v>$5,600.00</v>
+        <v>$3,064.79</v>
       </c>
       <c r="D10" t="str">
-        <v>$5,600.00</v>
+        <v>$3,064.79</v>
       </c>
       <c r="E10" t="str">
-        <v>AETNA 07/02/2025</v>
+        <v>RFMS 07/02/2025</v>
       </c>
       <c r="F10" t="str">
-        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
+        <v>NDC CRT#A D# D#</v>
       </c>
       <c r="G10" t="str">
         <v>Exact</v>
@@ -1055,45 +1053,47 @@
         <v>07/02/2025</v>
       </c>
       <c r="C12" t="str">
-        <v>$3,064.79</v>
+        <v>$5,600.00</v>
       </c>
       <c r="D12" t="str">
-        <v>$3,064.79</v>
+        <v>$5,600.00</v>
       </c>
       <c r="E12" t="str">
-        <v>RFMS 07/02/2025</v>
+        <v>AETNA 07/02/2025</v>
       </c>
       <c r="F12" t="str">
-        <v>NDC CRT#A D# D#</v>
+        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
       </c>
       <c r="G12" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" xml:space="preserve">
       <c r="A13" t="str">
         <v>07/02/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>07/02/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="C13" t="str">
-        <v>$111.86</v>
+        <v>$17,930.91</v>
       </c>
       <c r="D13" t="str">
-        <v>$111.86</v>
-      </c>
-      <c r="E13" t="str">
-        <v>VETERAN FAMILY MEMBER PROGRAM 07/02/2025</v>
-      </c>
-      <c r="F13" t="str">
-        <v>TREAS MISC PAY</v>
+        <v>$17,930.91</v>
+      </c>
+      <c r="E13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $30.00 (ACH 7/2/2025 | 7/2)
+2: $17,900.91 (Deposit 7/2/2025 | 7/2)</v>
+      </c>
+      <c r="F13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $6,022.00 (Glen Brook Rehab Settlement | 7/3)
+2: $11,908.91 (Glen Brook Rehab Settlement | 7/3)</v>
       </c>
       <c r="G13" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="14" xml:space="preserve">
+        <v>Many-to-Many</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" t="str">
         <v>07/03/2025</v>
       </c>
@@ -1101,92 +1101,92 @@
         <v>07/07/2025</v>
       </c>
       <c r="C14" t="str">
+        <v>$111.58</v>
+      </c>
+      <c r="D14" t="str">
+        <v>$111.58</v>
+      </c>
+      <c r="E14" t="str">
+        <v>WPS GHA - MAC J5 PART A 07/03/2025</v>
+      </c>
+      <c r="F14" t="str">
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="B15" t="str">
+        <v>07/08/2025</v>
+      </c>
+      <c r="C15" t="str">
+        <v>$3,966.81</v>
+      </c>
+      <c r="D15" t="str">
+        <v>$3,966.81</v>
+      </c>
+      <c r="E15" t="str">
+        <v>UPMC HEALTH PLAN, INC 07/03/2025</v>
+      </c>
+      <c r="F15" t="str">
+        <v>PAYABLES UPMC HEALTH PLAN TRN* * E* \</v>
+      </c>
+      <c r="G15" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="B16" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="C16" t="str">
+        <v>$8,127.07</v>
+      </c>
+      <c r="D16" t="str">
+        <v>$8,127.07</v>
+      </c>
+      <c r="E16" t="str">
+        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 07/03/2025</v>
+      </c>
+      <c r="F16" t="str">
+        <v>HCCLAIMPMT AARP Supplementa TRN* * * * \</v>
+      </c>
+      <c r="G16" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="17" xml:space="preserve">
+      <c r="A17" t="str">
+        <v>07/03/2025</v>
+      </c>
+      <c r="B17" t="str">
+        <v>07/07/2025</v>
+      </c>
+      <c r="C17" t="str">
         <v>$23,706.56</v>
       </c>
-      <c r="D14" t="str">
+      <c r="D17" t="str">
         <v>$23,706.56</v>
       </c>
-      <c r="E14" t="str" xml:space="preserve">
+      <c r="E17" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $1,082.00 (ACH 07/03/2025 | 7/3)
 2: $11,160.00 (ACH 07/03/2025 | 7/3)
 3: $185.00 (ACH 07/03/2025 | 7/3)
 4: $9,986.24 (ACH 07/03/2025 | 7/3)
 5: $1,293.32 (CC 07/03/2025 | 7/3)</v>
       </c>
-      <c r="F14" t="str">
+      <c r="F17" t="str">
         <v>Glen Brook Rehab Settlement</v>
       </c>
-      <c r="G14" t="str">
+      <c r="G17" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="B15" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="C15" t="str">
-        <v>$8,127.07</v>
-      </c>
-      <c r="D15" t="str">
-        <v>$8,127.07</v>
-      </c>
-      <c r="E15" t="str">
-        <v>AARP SUPPLEMENTAL HEALTH PLANS FROM UNITEDHEALTHCARE 07/03/2025</v>
-      </c>
-      <c r="F15" t="str">
-        <v>HCCLAIMPMT AARP Supplementa TRN* * * * \</v>
-      </c>
-      <c r="G15" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="B16" t="str">
-        <v>07/07/2025</v>
-      </c>
-      <c r="C16" t="str">
-        <v>$111.58</v>
-      </c>
-      <c r="D16" t="str">
-        <v>$111.58</v>
-      </c>
-      <c r="E16" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/03/2025</v>
-      </c>
-      <c r="F16" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
-      </c>
-      <c r="G16" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="B17" t="str">
-        <v>07/03/2025</v>
-      </c>
-      <c r="C17" t="str">
-        <v>$74,317.01</v>
-      </c>
-      <c r="D17" t="str">
-        <v>$74,317.01</v>
-      </c>
-      <c r="E17" t="str">
-        <v>RFMS 07/03/25</v>
-      </c>
-      <c r="F17" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
-      </c>
-      <c r="G17" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="18">
@@ -1194,19 +1194,19 @@
         <v>07/03/2025</v>
       </c>
       <c r="B18" t="str">
-        <v>07/08/2025</v>
+        <v>07/03/2025</v>
       </c>
       <c r="C18" t="str">
-        <v>$3,966.81</v>
+        <v>$74,317.01</v>
       </c>
       <c r="D18" t="str">
-        <v>$3,966.81</v>
+        <v>$74,317.01</v>
       </c>
       <c r="E18" t="str">
-        <v>UPMC HEALTH PLAN, INC 07/03/2025</v>
+        <v>RFMS 07/03/25</v>
       </c>
       <c r="F18" t="str">
-        <v>PAYABLES UPMC HEALTH PLAN TRN* * E* \</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G18" t="str">
         <v>Exact</v>
@@ -1272,16 +1272,16 @@
         <v>07/08/2025</v>
       </c>
       <c r="C21" t="str">
-        <v>$1,403.90</v>
+        <v>$374.47</v>
       </c>
       <c r="D21" t="str">
-        <v>$1,403.90</v>
+        <v>$374.47</v>
       </c>
       <c r="E21" t="str">
-        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/07/2025</v>
+        <v>WPS GHA - MAC J5 PART A 07/07/2025</v>
       </c>
       <c r="F21" t="str">
-        <v>HCCLAIMPMT PNC-ECHO TRN* * * \</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G21" t="str">
         <v>Exact</v>
@@ -1295,16 +1295,16 @@
         <v>07/08/2025</v>
       </c>
       <c r="C22" t="str">
-        <v>$374.47</v>
+        <v>$1,403.90</v>
       </c>
       <c r="D22" t="str">
-        <v>$374.47</v>
+        <v>$1,403.90</v>
       </c>
       <c r="E22" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/07/2025</v>
+        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/07/2025</v>
       </c>
       <c r="F22" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>HCCLAIMPMT PNC-ECHO TRN* * * \</v>
       </c>
       <c r="G22" t="str">
         <v>Exact</v>
@@ -1341,16 +1341,16 @@
         <v>07/09/2025</v>
       </c>
       <c r="C24" t="str">
-        <v>$543,180.38</v>
+        <v>$1,680.93</v>
       </c>
       <c r="D24" t="str">
-        <v>$543,180.38</v>
+        <v>$1,680.93</v>
       </c>
       <c r="E24" t="str">
-        <v>PA HEALTH &amp; WELLNESS 07/08/2025</v>
+        <v>MCR 07/08/2025</v>
       </c>
       <c r="F24" t="str">
-        <v>HCCLAIMPMT PA CLAIMS TRN* * * \</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G24" t="str">
         <v>Exact</v>
@@ -1361,19 +1361,19 @@
         <v>07/08/2025</v>
       </c>
       <c r="B25" t="str">
-        <v>07/09/2025</v>
+        <v>07/11/2025</v>
       </c>
       <c r="C25" t="str">
-        <v>$1,680.93</v>
+        <v>$1,877.06</v>
       </c>
       <c r="D25" t="str">
-        <v>$1,680.93</v>
+        <v>$1,877.06</v>
       </c>
       <c r="E25" t="str">
-        <v>MCR 07/08/2025</v>
+        <v>UPMC 07/08/2025</v>
       </c>
       <c r="F25" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>PAYABLES UPMC HEALTH PLAN TRN* * E* \</v>
       </c>
       <c r="G25" t="str">
         <v>Exact</v>
@@ -1384,19 +1384,19 @@
         <v>07/08/2025</v>
       </c>
       <c r="B26" t="str">
-        <v>07/11/2025</v>
+        <v>07/09/2025</v>
       </c>
       <c r="C26" t="str">
-        <v>$1,877.06</v>
+        <v>$543,180.38</v>
       </c>
       <c r="D26" t="str">
-        <v>$1,877.06</v>
+        <v>$543,180.38</v>
       </c>
       <c r="E26" t="str">
-        <v>UPMC 07/08/2025</v>
+        <v>PA HEALTH &amp; WELLNESS 07/08/2025</v>
       </c>
       <c r="F26" t="str">
-        <v>PAYABLES UPMC HEALTH PLAN TRN* * E* \</v>
+        <v>HCCLAIMPMT PA CLAIMS TRN* * * \</v>
       </c>
       <c r="G26" t="str">
         <v>Exact</v>
@@ -1425,51 +1425,51 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="28" xml:space="preserve">
+    <row r="28">
       <c r="A28" t="str">
         <v>07/09/2025</v>
       </c>
       <c r="B28" t="str">
+        <v>07/09/2025</v>
+      </c>
+      <c r="C28" t="str">
+        <v>$6,445.00</v>
+      </c>
+      <c r="D28" t="str">
+        <v>$6,445.00</v>
+      </c>
+      <c r="E28" t="str">
+        <v>RFMS 07/09/2025</v>
+      </c>
+      <c r="F28" t="str">
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+      </c>
+      <c r="G28" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="29" xml:space="preserve">
+      <c r="A29" t="str">
+        <v>07/09/2025</v>
+      </c>
+      <c r="B29" t="str">
         <v>07/10/2025</v>
       </c>
-      <c r="C28" t="str">
+      <c r="C29" t="str">
         <v>$13,347.00</v>
       </c>
-      <c r="D28" t="str">
+      <c r="D29" t="str">
         <v>$13,347.00</v>
       </c>
-      <c r="E28" t="str" xml:space="preserve">
+      <c r="E29" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $12,090.00 (ACH 7/9/2025 | 7/9)
 2: $1,257.00 (CC 7/9/2025 | 7/9)</v>
       </c>
-      <c r="F28" t="str">
+      <c r="F29" t="str">
         <v>Glen Brook Rehab Settlement</v>
       </c>
-      <c r="G28" t="str">
+      <c r="G29" t="str">
         <v>Many-to-One</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="str">
-        <v>07/09/2025</v>
-      </c>
-      <c r="B29" t="str">
-        <v>07/09/2025</v>
-      </c>
-      <c r="C29" t="str">
-        <v>$6,445.00</v>
-      </c>
-      <c r="D29" t="str">
-        <v>$6,445.00</v>
-      </c>
-      <c r="E29" t="str">
-        <v>RFMS 07/09/2025</v>
-      </c>
-      <c r="F29" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
-      </c>
-      <c r="G29" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="30">
@@ -1495,7 +1495,7 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" xml:space="preserve">
       <c r="A31" t="str">
         <v>07/10/2025</v>
       </c>
@@ -1503,22 +1503,23 @@
         <v>07/11/2025</v>
       </c>
       <c r="C31" t="str">
-        <v>$2,112.70</v>
+        <v>$1,753.40</v>
       </c>
       <c r="D31" t="str">
-        <v>$2,112.70</v>
-      </c>
-      <c r="E31" t="str">
-        <v>CC 7/10/2025</v>
+        <v>$1,753.40</v>
+      </c>
+      <c r="E31" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $924.00 (ACH 7/10/2025 | 7/10)
+2: $829.40 (ACH 7/10/2025 | 7/10)</v>
       </c>
       <c r="F31" t="str">
-        <v>BANKCARD BTOT DEP</v>
+        <v>Glen Brook Rehab Settlement</v>
       </c>
       <c r="G31" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="32" xml:space="preserve">
+        <v>Many-to-One</v>
+      </c>
+    </row>
+    <row r="32">
       <c r="A32" t="str">
         <v>07/10/2025</v>
       </c>
@@ -1526,20 +1527,19 @@
         <v>07/11/2025</v>
       </c>
       <c r="C32" t="str">
-        <v>$1,753.40</v>
+        <v>$2,112.70</v>
       </c>
       <c r="D32" t="str">
-        <v>$1,753.40</v>
-      </c>
-      <c r="E32" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $924.00 (ACH 7/10/2025 | 7/10)
-2: $829.40 (ACH 7/10/2025 | 7/10)</v>
+        <v>$2,112.70</v>
+      </c>
+      <c r="E32" t="str">
+        <v>CC 7/10/2025</v>
       </c>
       <c r="F32" t="str">
-        <v>Glen Brook Rehab Settlement</v>
+        <v>BANKCARD BTOT DEP</v>
       </c>
       <c r="G32" t="str">
-        <v>Many-to-One</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="33">
@@ -1570,19 +1570,19 @@
         <v>07/12/2025</v>
       </c>
       <c r="B34" t="str">
-        <v>07/14/2025</v>
+        <v>07/15/2025</v>
       </c>
       <c r="C34" t="str">
-        <v>$1,362.00</v>
+        <v>$929.61</v>
       </c>
       <c r="D34" t="str">
-        <v>$1,362.00</v>
+        <v>$929.61</v>
       </c>
       <c r="E34" t="str">
-        <v>CC 7/12/2025</v>
+        <v>ACH 7/12/2025</v>
       </c>
       <c r="F34" t="str">
-        <v>BANKCARD BTOT DEP</v>
+        <v>Glen Brook Rehab Settlement</v>
       </c>
       <c r="G34" t="str">
         <v>Exact</v>
@@ -1593,19 +1593,19 @@
         <v>07/12/2025</v>
       </c>
       <c r="B35" t="str">
-        <v>07/15/2025</v>
+        <v>07/14/2025</v>
       </c>
       <c r="C35" t="str">
-        <v>$929.61</v>
+        <v>$1,362.00</v>
       </c>
       <c r="D35" t="str">
-        <v>$929.61</v>
+        <v>$1,362.00</v>
       </c>
       <c r="E35" t="str">
-        <v>ACH 7/12/2025</v>
+        <v>CC 7/12/2025</v>
       </c>
       <c r="F35" t="str">
-        <v>Glen Brook Rehab Settlement</v>
+        <v>BANKCARD BTOT DEP</v>
       </c>
       <c r="G35" t="str">
         <v>Exact</v>
@@ -1657,7 +1657,7 @@
         <v>Exact</v>
       </c>
     </row>
-    <row r="38" xml:space="preserve">
+    <row r="38">
       <c r="A38" t="str">
         <v>07/15/2025</v>
       </c>
@@ -1665,164 +1665,164 @@
         <v>07/16/2025</v>
       </c>
       <c r="C38" t="str">
+        <v>$631.89</v>
+      </c>
+      <c r="D38" t="str">
+        <v>$631.89</v>
+      </c>
+      <c r="E38" t="str">
+        <v>MCR 07/15/2025</v>
+      </c>
+      <c r="F38" t="str">
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+      </c>
+      <c r="G38" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="B39" t="str">
+        <v>07/18/2025</v>
+      </c>
+      <c r="C39" t="str">
+        <v>$709.16</v>
+      </c>
+      <c r="D39" t="str">
+        <v>$709.16</v>
+      </c>
+      <c r="E39" t="str">
+        <v>HUMANA INC. 07/15/2025</v>
+      </c>
+      <c r="F39" t="str">
+        <v>HCCLAIMPMT HUMANA INS CO TRN* * * \</v>
+      </c>
+      <c r="G39" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="B40" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="C40" t="str">
+        <v>$712.93</v>
+      </c>
+      <c r="D40" t="str">
+        <v>$712.93</v>
+      </c>
+      <c r="E40" t="str">
+        <v>GEISINGER INDEMNITY INS CO 07/15/2025</v>
+      </c>
+      <c r="F40" t="str">
+        <v>HCCLAIMPMT GEISINGER INDEMN TRN* * * * IN~</v>
+      </c>
+      <c r="G40" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="B41" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="C41" t="str">
+        <v>$785.70</v>
+      </c>
+      <c r="D41" t="str">
+        <v>$785.70</v>
+      </c>
+      <c r="E41" t="str">
+        <v>RFMS 7/15/2025</v>
+      </c>
+      <c r="F41" t="str">
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+      </c>
+      <c r="G41" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="B42" t="str">
+        <v>07/21/2025</v>
+      </c>
+      <c r="C42" t="str">
+        <v>$5,588.21</v>
+      </c>
+      <c r="D42" t="str">
+        <v>$5,588.21</v>
+      </c>
+      <c r="E42" t="str">
+        <v>Deposit 07/15/2025</v>
+      </c>
+      <c r="F42" t="str">
+        <v>Glen Brook Rehab Settlement</v>
+      </c>
+      <c r="G42" t="str">
+        <v>Exact</v>
+      </c>
+    </row>
+    <row r="43" xml:space="preserve">
+      <c r="A43" t="str">
+        <v>07/15/2025</v>
+      </c>
+      <c r="B43" t="str">
+        <v>07/16/2025</v>
+      </c>
+      <c r="C43" t="str">
         <v>$41,761.63</v>
       </c>
-      <c r="D38" t="str">
+      <c r="D43" t="str">
         <v>$41,761.63</v>
       </c>
-      <c r="E38" t="str" xml:space="preserve">
+      <c r="E43" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $20,460.47 (Deposit 07/15/2025 | 7/15)
 2: $9,587.16 (Deposit 07/15/2025 | 7/15)
 3: $11,714.00 (Deposit 07/15/2025 | 7/15)</v>
       </c>
-      <c r="F38" t="str" xml:space="preserve">
+      <c r="F43" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $14,294.98 (Glen Brook Rehab Settlement | 7/16)
 2: $27,466.65 (Glen Brook Rehab Settlement | 7/16)</v>
       </c>
-      <c r="G38" t="str">
+      <c r="G43" t="str">
         <v>Many-to-Many</v>
       </c>
     </row>
-    <row r="39" xml:space="preserve">
-      <c r="A39" t="str" xml:space="preserve">
+    <row r="44" xml:space="preserve">
+      <c r="A44" t="str" xml:space="preserve">
         <v xml:space="preserve">07/15/2025
 -
 07/16/2025</v>
       </c>
-      <c r="B39" t="str">
+      <c r="B44" t="str">
         <v>07/17/2025</v>
       </c>
-      <c r="C39" t="str">
+      <c r="C44" t="str">
         <v>$67,144.33</v>
       </c>
-      <c r="D39" t="str">
+      <c r="D44" t="str">
         <v>$67,144.33</v>
       </c>
-      <c r="E39" t="str" xml:space="preserve">
+      <c r="E44" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $63,674.33 (Deposit 07/16/2025 | 7/16)
 2: $3,470.00 (ACH 07/15/25 | 7/15)</v>
       </c>
-      <c r="F39" t="str" xml:space="preserve">
+      <c r="F44" t="str" xml:space="preserve">
         <v xml:space="preserve">1: $16,028.00 (Glen Brook Rehab Settlement | 7/17)
 2: $51,116.33 (Glen Brook Rehab Settlement | 7/17)</v>
       </c>
-      <c r="G39" t="str">
+      <c r="G44" t="str">
         <v>Many-to-Many</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="B40" t="str">
-        <v>07/21/2025</v>
-      </c>
-      <c r="C40" t="str">
-        <v>$5,588.21</v>
-      </c>
-      <c r="D40" t="str">
-        <v>$5,588.21</v>
-      </c>
-      <c r="E40" t="str">
-        <v>Deposit 07/15/2025</v>
-      </c>
-      <c r="F40" t="str">
-        <v>Glen Brook Rehab Settlement</v>
-      </c>
-      <c r="G40" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="B41" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="C41" t="str">
-        <v>$712.93</v>
-      </c>
-      <c r="D41" t="str">
-        <v>$712.93</v>
-      </c>
-      <c r="E41" t="str">
-        <v>GEISINGER INDEMNITY INS CO 07/15/2025</v>
-      </c>
-      <c r="F41" t="str">
-        <v>HCCLAIMPMT GEISINGER INDEMN TRN* * * * IN~</v>
-      </c>
-      <c r="G41" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="B42" t="str">
-        <v>07/18/2025</v>
-      </c>
-      <c r="C42" t="str">
-        <v>$709.16</v>
-      </c>
-      <c r="D42" t="str">
-        <v>$709.16</v>
-      </c>
-      <c r="E42" t="str">
-        <v>HUMANA INC. 07/15/2025</v>
-      </c>
-      <c r="F42" t="str">
-        <v>HCCLAIMPMT HUMANA INS CO TRN* * * \</v>
-      </c>
-      <c r="G42" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="B43" t="str">
-        <v>07/16/2025</v>
-      </c>
-      <c r="C43" t="str">
-        <v>$631.89</v>
-      </c>
-      <c r="D43" t="str">
-        <v>$631.89</v>
-      </c>
-      <c r="E43" t="str">
-        <v>MCR 07/15/2025</v>
-      </c>
-      <c r="F43" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
-      </c>
-      <c r="G43" t="str">
-        <v>Exact</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="B44" t="str">
-        <v>07/15/2025</v>
-      </c>
-      <c r="C44" t="str">
-        <v>$785.70</v>
-      </c>
-      <c r="D44" t="str">
-        <v>$785.70</v>
-      </c>
-      <c r="E44" t="str">
-        <v>RFMS 7/15/2025</v>
-      </c>
-      <c r="F44" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
-      </c>
-      <c r="G44" t="str">
-        <v>Exact</v>
       </c>
     </row>
     <row r="45">
@@ -1879,16 +1879,16 @@
         <v>07/16/2025</v>
       </c>
       <c r="C47" t="str">
-        <v>$18,900.00</v>
+        <v>$2,484.40</v>
       </c>
       <c r="D47" t="str">
-        <v>$18,900.00</v>
+        <v>$2,484.40</v>
       </c>
       <c r="E47" t="str">
-        <v>AETNA 07/16/2025</v>
+        <v>MCD PA 07/16/2025</v>
       </c>
       <c r="F47" t="str">
-        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
+        <v>PROMISE MA COMM OF PA TRN* * * \</v>
       </c>
       <c r="G47" t="str">
         <v>Exact</v>
@@ -1899,19 +1899,19 @@
         <v>07/16/2025</v>
       </c>
       <c r="B48" t="str">
-        <v>07/17/2025</v>
+        <v>07/16/2025</v>
       </c>
       <c r="C48" t="str">
-        <v>$4,180.00</v>
+        <v>$3,698.00</v>
       </c>
       <c r="D48" t="str">
-        <v>$4,180.00</v>
+        <v>$3,698.00</v>
       </c>
       <c r="E48" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/16/2025</v>
+        <v>RFMS 07/16/2025</v>
       </c>
       <c r="F48" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G48" t="str">
         <v>Exact</v>
@@ -1922,19 +1922,19 @@
         <v>07/16/2025</v>
       </c>
       <c r="B49" t="str">
-        <v>07/16/2025</v>
+        <v>07/17/2025</v>
       </c>
       <c r="C49" t="str">
-        <v>$3,698.00</v>
+        <v>$4,180.00</v>
       </c>
       <c r="D49" t="str">
-        <v>$3,698.00</v>
+        <v>$4,180.00</v>
       </c>
       <c r="E49" t="str">
-        <v>RFMS 07/16/2025</v>
+        <v>WPS GHA - MAC J5 PART A 07/16/2025</v>
       </c>
       <c r="F49" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G49" t="str">
         <v>Exact</v>
@@ -1948,16 +1948,16 @@
         <v>07/16/2025</v>
       </c>
       <c r="C50" t="str">
-        <v>$2,484.40</v>
+        <v>$18,900.00</v>
       </c>
       <c r="D50" t="str">
-        <v>$2,484.40</v>
+        <v>$18,900.00</v>
       </c>
       <c r="E50" t="str">
-        <v>MCD PA 07/16/2025</v>
+        <v>AETNA 07/16/2025</v>
       </c>
       <c r="F50" t="str">
-        <v>PROMISE MA COMM OF PA TRN* * * \</v>
+        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
       </c>
       <c r="G50" t="str">
         <v>Exact</v>
@@ -2086,19 +2086,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B56" t="str">
-        <v>07/23/2025</v>
+        <v>07/22/2025</v>
       </c>
       <c r="C56" t="str">
-        <v>$2,711.85</v>
+        <v>$175.06</v>
       </c>
       <c r="D56" t="str">
-        <v>$2,711.85</v>
+        <v>$175.06</v>
       </c>
       <c r="E56" t="str">
-        <v>ACH 7/22/2025</v>
+        <v>GEISINGER HEALTH PLAN 07/22/2025</v>
       </c>
       <c r="F56" t="str">
-        <v>Glen Brook Rehab Settlement</v>
+        <v>HCCLAIMPMT GEISINGER HEALTH TRN* * * * HP~</v>
       </c>
       <c r="G56" t="str">
         <v>Exact</v>
@@ -2109,19 +2109,19 @@
         <v>07/22/2025</v>
       </c>
       <c r="B57" t="str">
-        <v>07/22/2025</v>
+        <v>07/23/2025</v>
       </c>
       <c r="C57" t="str">
-        <v>$175.06</v>
+        <v>$2,711.85</v>
       </c>
       <c r="D57" t="str">
-        <v>$175.06</v>
+        <v>$2,711.85</v>
       </c>
       <c r="E57" t="str">
-        <v>GEISINGER HEALTH PLAN 07/22/2025</v>
+        <v>ACH 7/22/2025</v>
       </c>
       <c r="F57" t="str">
-        <v>HCCLAIMPMT GEISINGER HEALTH TRN* * * * HP~</v>
+        <v>Glen Brook Rehab Settlement</v>
       </c>
       <c r="G57" t="str">
         <v>Exact</v>
@@ -2158,16 +2158,16 @@
         <v>07/23/2025</v>
       </c>
       <c r="C59" t="str">
-        <v>$5,219.00</v>
+        <v>$595.09</v>
       </c>
       <c r="D59" t="str">
-        <v>$5,219.00</v>
+        <v>$595.09</v>
       </c>
       <c r="E59" t="str">
         <v>RFMS 7/23/2025</v>
       </c>
       <c r="F59" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+        <v>NDC CRT#BC W#CC W#CC</v>
       </c>
       <c r="G59" t="str">
         <v>Exact</v>
@@ -2181,16 +2181,16 @@
         <v>07/23/2025</v>
       </c>
       <c r="C60" t="str">
-        <v>$595.09</v>
+        <v>$5,219.00</v>
       </c>
       <c r="D60" t="str">
-        <v>$595.09</v>
+        <v>$5,219.00</v>
       </c>
       <c r="E60" t="str">
         <v>RFMS 7/23/2025</v>
       </c>
       <c r="F60" t="str">
-        <v>NDC CRT#BC W#CC W#CC</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G60" t="str">
         <v>Exact</v>
@@ -2274,16 +2274,16 @@
         <v>07/28/2025</v>
       </c>
       <c r="C64" t="str">
-        <v>$323,719.29</v>
+        <v>$14,726.20</v>
       </c>
       <c r="D64" t="str">
-        <v>$323,719.29</v>
+        <v>$14,726.20</v>
       </c>
       <c r="E64" t="str">
-        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/25/2025</v>
+        <v>WPS GHA - MAC J5 PART A 07/25/2025</v>
       </c>
       <c r="F64" t="str">
-        <v>HCCLAIMPMT PNC-ECHO TRN* * * \</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G64" t="str">
         <v>Exact</v>
@@ -2297,16 +2297,16 @@
         <v>07/28/2025</v>
       </c>
       <c r="C65" t="str">
-        <v>$14,726.20</v>
+        <v>$323,719.29</v>
       </c>
       <c r="D65" t="str">
-        <v>$14,726.20</v>
+        <v>$323,719.29</v>
       </c>
       <c r="E65" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/25/2025</v>
+        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/25/2025</v>
       </c>
       <c r="F65" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>HCCLAIMPMT PNC-ECHO TRN* * * \</v>
       </c>
       <c r="G65" t="str">
         <v>Exact</v>
@@ -2373,16 +2373,16 @@
         <v>07/30/2025</v>
       </c>
       <c r="C68" t="str">
-        <v>$1,351.00</v>
+        <v>$93.78</v>
       </c>
       <c r="D68" t="str">
-        <v>$1,351.00</v>
+        <v>$93.78</v>
       </c>
       <c r="E68" t="str">
-        <v>ACH 07/29/25</v>
+        <v>WPS GHA - MAC J5 PART A 07/29/2025</v>
       </c>
       <c r="F68" t="str">
-        <v>Glen Brook Rehab Settlement</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G68" t="str">
         <v>Exact</v>
@@ -2416,19 +2416,19 @@
         <v>07/29/2025</v>
       </c>
       <c r="B70" t="str">
-        <v>07/29/2025</v>
+        <v>07/30/2025</v>
       </c>
       <c r="C70" t="str">
-        <v>$1,647.70</v>
+        <v>$1,351.00</v>
       </c>
       <c r="D70" t="str">
-        <v>$1,647.70</v>
+        <v>$1,351.00</v>
       </c>
       <c r="E70" t="str">
-        <v>GEISINGER HEALTH PLAN 07/29/2025</v>
+        <v>ACH 07/29/25</v>
       </c>
       <c r="F70" t="str">
-        <v>HCCLAIMPMT GEISINGER HEALTH TRN* * * * HP~</v>
+        <v>Glen Brook Rehab Settlement</v>
       </c>
       <c r="G70" t="str">
         <v>Exact</v>
@@ -2439,46 +2439,45 @@
         <v>07/29/2025</v>
       </c>
       <c r="B71" t="str">
-        <v>07/30/2025</v>
+        <v>07/29/2025</v>
       </c>
       <c r="C71" t="str">
-        <v>$93.78</v>
+        <v>$1,647.70</v>
       </c>
       <c r="D71" t="str">
-        <v>$93.78</v>
+        <v>$1,647.70</v>
       </c>
       <c r="E71" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/29/2025</v>
+        <v>GEISINGER HEALTH PLAN 07/29/2025</v>
       </c>
       <c r="F71" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>HCCLAIMPMT GEISINGER HEALTH TRN* * * * HP~</v>
       </c>
       <c r="G71" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="72" xml:space="preserve">
+    <row r="72">
       <c r="A72" t="str">
         <v>07/30/2025</v>
       </c>
       <c r="B72" t="str">
-        <v>07/31/2025</v>
+        <v>07/30/2025</v>
       </c>
       <c r="C72" t="str">
-        <v>$15,473.99</v>
+        <v>$57.18</v>
       </c>
       <c r="D72" t="str">
-        <v>$15,473.99</v>
-      </c>
-      <c r="E72" t="str" xml:space="preserve">
-        <v xml:space="preserve">1: $473.99 (ACH 7/30/2025 | 7/30)
-2: $15,000.00 (ACH 07/30/2025 | 7/30)</v>
+        <v>$57.18</v>
+      </c>
+      <c r="E72" t="str">
+        <v>AETNA 07/30/2025</v>
       </c>
       <c r="F72" t="str">
-        <v>Glen Brook Rehab Settlement</v>
+        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
       </c>
       <c r="G72" t="str">
-        <v>Many-to-One</v>
+        <v>Exact</v>
       </c>
     </row>
     <row r="73">
@@ -2486,25 +2485,25 @@
         <v>07/30/2025</v>
       </c>
       <c r="B73" t="str">
-        <v>07/30/2025</v>
+        <v>07/31/2025</v>
       </c>
       <c r="C73" t="str">
-        <v>$57.18</v>
+        <v>$7,660.00</v>
       </c>
       <c r="D73" t="str">
-        <v>$57.18</v>
+        <v>$7,660.00</v>
       </c>
       <c r="E73" t="str">
-        <v>AETNA 07/30/2025</v>
+        <v>WPS GHA - MAC J5 PART A 07/30/2025</v>
       </c>
       <c r="F73" t="str">
-        <v>HCCLAIMPMT AETNA AS TRN* * * \</v>
+        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
       </c>
       <c r="G73" t="str">
         <v>Exact</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" xml:space="preserve">
       <c r="A74" t="str">
         <v>07/30/2025</v>
       </c>
@@ -2512,19 +2511,20 @@
         <v>07/31/2025</v>
       </c>
       <c r="C74" t="str">
-        <v>$7,660.00</v>
+        <v>$15,473.99</v>
       </c>
       <c r="D74" t="str">
-        <v>$7,660.00</v>
-      </c>
-      <c r="E74" t="str">
-        <v>WPS GHA - MAC J5 PART A 07/30/2025</v>
+        <v>$15,473.99</v>
+      </c>
+      <c r="E74" t="str" xml:space="preserve">
+        <v xml:space="preserve">1: $473.99 (ACH 7/30/2025 | 7/30)
+2: $15,000.00 (ACH 07/30/2025 | 7/30)</v>
       </c>
       <c r="F74" t="str">
-        <v>HCCLAIMPMT WISCONSIN PHYSIC TRN* * EFT* * ~</v>
+        <v>Glen Brook Rehab Settlement</v>
       </c>
       <c r="G74" t="str">
-        <v>Exact</v>
+        <v>Many-to-One</v>
       </c>
     </row>
     <row r="75">
@@ -2535,16 +2535,16 @@
         <v>07/31/2025</v>
       </c>
       <c r="C75" t="str">
-        <v>$11,038.95</v>
+        <v>$1,499.36</v>
       </c>
       <c r="D75" t="str">
-        <v>$11,038.95</v>
+        <v>$1,499.36</v>
       </c>
       <c r="E75" t="str">
-        <v>UHC 07/31/2025</v>
+        <v>RFMS 7/31/2025</v>
       </c>
       <c r="F75" t="str">
-        <v>HCCLAIMPMT UnitedHealthcare TRN* * T* * \</v>
+        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
       </c>
       <c r="G75" t="str">
         <v>Exact</v>
@@ -2558,16 +2558,16 @@
         <v>07/31/2025</v>
       </c>
       <c r="C76" t="str">
-        <v>$1,499.36</v>
+        <v>$11,038.95</v>
       </c>
       <c r="D76" t="str">
-        <v>$1,499.36</v>
+        <v>$11,038.95</v>
       </c>
       <c r="E76" t="str">
-        <v>RFMS 7/31/2025</v>
+        <v>UHC 07/31/2025</v>
       </c>
       <c r="F76" t="str">
-        <v>NDC CRT# DIRECT_DEP DIRECT_DEP</v>
+        <v>HCCLAIMPMT UnitedHealthcare TRN* * T* * \</v>
       </c>
       <c r="G76" t="str">
         <v>Exact</v>
@@ -2603,10 +2603,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$3,926.62</v>
+        <v>$2,197.95</v>
       </c>
       <c r="C2" t="str">
-        <v>Deposit 07/23/2025</v>
+        <v>ACH 7/23/2025</v>
       </c>
       <c r="D2" t="str">
         <v>Unmatched</v>
@@ -2617,10 +2617,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$2,197.95</v>
+        <v>$200.00</v>
       </c>
       <c r="C3" t="str">
-        <v>ACH 7/23/2025</v>
+        <v>Apploi 07/23/2025</v>
       </c>
       <c r="D3" t="str">
         <v>Unmatched</v>
@@ -2631,7 +2631,7 @@
         <v>07/23/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$47,334.98</v>
+        <v>$3,926.62</v>
       </c>
       <c r="C4" t="str">
         <v>Deposit 07/23/2025</v>
@@ -2645,10 +2645,10 @@
         <v>07/23/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$200.00</v>
+        <v>$47,334.98</v>
       </c>
       <c r="C5" t="str">
-        <v>Apploi 07/23/2025</v>
+        <v>Deposit 07/23/2025</v>
       </c>
       <c r="D5" t="str">
         <v>Unmatched</v>
@@ -2748,10 +2748,10 @@
         <v>07/03/2025</v>
       </c>
       <c r="B2" t="str">
-        <v>$735.00</v>
+        <v>-$735.00</v>
       </c>
       <c r="C2" t="str">
-        <v>RFMS 07/03/25 (Slusser, Laura)</v>
+        <v>Batch#4912 - RFMS 07/03/25 (Slusser, Laura) * Reversals *</v>
       </c>
     </row>
     <row r="3">
@@ -2759,10 +2759,10 @@
         <v>07/03/2025</v>
       </c>
       <c r="B3" t="str">
-        <v>$-735.00</v>
+        <v>$735.00</v>
       </c>
       <c r="C3" t="str">
-        <v>Batch#4912 - RFMS 07/03/25 (Slusser, Laura) * Reversals *</v>
+        <v>RFMS 07/03/25 (Slusser, Laura)</v>
       </c>
     </row>
     <row r="4">
@@ -2770,10 +2770,10 @@
         <v>07/09/2025</v>
       </c>
       <c r="B4" t="str">
-        <v>$36,168.26</v>
+        <v>-$36,168.26</v>
       </c>
       <c r="C4" t="str">
-        <v>DEPARTMENT OF HUMAN SERVICES 07/09/2025</v>
+        <v>Batch#4919 - DEPARTMENT OF HUMAN SERVICES 07/ 09/2025 * Rever</v>
       </c>
     </row>
     <row r="5">
@@ -2781,10 +2781,10 @@
         <v>07/09/2025</v>
       </c>
       <c r="B5" t="str">
-        <v>$-36,168.26</v>
+        <v>$36,168.26</v>
       </c>
       <c r="C5" t="str">
-        <v>Batch#4919 - DEPARTMENT OF HUMAN SERVICES 07/ 09/2025 * Rever</v>
+        <v>DEPARTMENT OF HUMAN SERVICES 07/09/2025</v>
       </c>
     </row>
     <row r="6">
@@ -2792,10 +2792,10 @@
         <v>07/10/2025</v>
       </c>
       <c r="B6" t="str">
-        <v>$2,112.70</v>
+        <v>-$2,112.70</v>
       </c>
       <c r="C6" t="str">
-        <v>CC 7/10/2025</v>
+        <v>Batch#4954 - CC 7/10/2025 * Reversals *</v>
       </c>
     </row>
     <row r="7">
@@ -2803,10 +2803,10 @@
         <v>07/10/2025</v>
       </c>
       <c r="B7" t="str">
-        <v>$-2,112.70</v>
+        <v>$2,112.70</v>
       </c>
       <c r="C7" t="str">
-        <v>Batch#4954 - CC 7/10/2025 * Reversals *</v>
+        <v>CC 7/10/2025</v>
       </c>
     </row>
     <row r="8">
@@ -2814,10 +2814,10 @@
         <v>07/11/2025</v>
       </c>
       <c r="B8" t="str">
-        <v>$1.00</v>
+        <v>-$1.00</v>
       </c>
       <c r="C8" t="str">
-        <v>AMERIHEALTH 07/11/2025 [Code CS]</v>
+        <v>Batch#4957 - AMERIHEALTH 07/11/2025 [Code CS] * Reversals *</v>
       </c>
     </row>
     <row r="9">
@@ -2825,10 +2825,10 @@
         <v>07/11/2025</v>
       </c>
       <c r="B9" t="str">
-        <v>$-1.00</v>
+        <v>$1.00</v>
       </c>
       <c r="C9" t="str">
-        <v>Batch#4957 - AMERIHEALTH 07/11/2025 [Code CS] * Reversals *</v>
+        <v>AMERIHEALTH 07/11/2025 [Code CS]</v>
       </c>
     </row>
     <row r="10">
@@ -2836,10 +2836,10 @@
         <v>07/15/2025</v>
       </c>
       <c r="B10" t="str">
-        <v>$2,008.72</v>
+        <v>-$2,008.72</v>
       </c>
       <c r="C10" t="str">
-        <v>AMERIHEALTH 07/15/2025 [Code CS]</v>
+        <v>Batch#4950 - AMERIHEALTH 07/15/2025 [Code CS] * Reversals *</v>
       </c>
     </row>
     <row r="11">
@@ -2847,10 +2847,10 @@
         <v>07/15/2025</v>
       </c>
       <c r="B11" t="str">
-        <v>$-2,008.72</v>
+        <v>$2,008.72</v>
       </c>
       <c r="C11" t="str">
-        <v>Batch#4950 - AMERIHEALTH 07/15/2025 [Code CS] * Reversals *</v>
+        <v>AMERIHEALTH 07/15/2025 [Code CS]</v>
       </c>
     </row>
     <row r="12">
@@ -2858,10 +2858,10 @@
         <v>07/22/2025</v>
       </c>
       <c r="B12" t="str">
-        <v>$646.19</v>
+        <v>-$646.19</v>
       </c>
       <c r="C12" t="str">
-        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/22/2025</v>
+        <v>Batch#4984 - AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>07/22/2025</v>
       </c>
       <c r="B13" t="str">
-        <v>$-646.19</v>
+        <v>$646.19</v>
       </c>
       <c r="C13" t="str">
-        <v>Batch#4984 - AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES</v>
+        <v>AMERIHEALTH CARITAS PA COMMUNITY HEALTHCHOICES 07/22/2025</v>
       </c>
     </row>
   </sheetData>
@@ -3180,7 +3180,7 @@
         <v>07/15/2025</v>
       </c>
       <c r="B18" t="str">
-        <v>$1,642.54</v>
+        <v>$188.98</v>
       </c>
       <c r="C18" t="str">
         <v>9999</v>
@@ -3197,7 +3197,7 @@
         <v>07/15/2025</v>
       </c>
       <c r="B19" t="str">
-        <v>$36,212.97</v>
+        <v>$1,642.54</v>
       </c>
       <c r="C19" t="str">
         <v>9999</v>
@@ -3214,7 +3214,7 @@
         <v>07/15/2025</v>
       </c>
       <c r="B20" t="str">
-        <v>$188.98</v>
+        <v>$36,212.97</v>
       </c>
       <c r="C20" t="str">
         <v>9999</v>
@@ -3537,7 +3537,7 @@
         <v>07/30/2025</v>
       </c>
       <c r="B39" t="str">
-        <v>$1,528.11</v>
+        <v>$188.98</v>
       </c>
       <c r="C39" t="str">
         <v>9999</v>
@@ -3554,7 +3554,7 @@
         <v>07/30/2025</v>
       </c>
       <c r="B40" t="str">
-        <v>$188.98</v>
+        <v>$1,528.11</v>
       </c>
       <c r="C40" t="str">
         <v>9999</v>
